--- a/Confluence/uc_metadata_standards_v4.xlsx
+++ b/Confluence/uc_metadata_standards_v4.xlsx
@@ -1356,12 +1356,12 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>layer</t>
+          <t>capability</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>sandbox · reference · core_model · core · analytics · products · consumer</t>
+          <t>collateral_management · liquidity_funding_risk · counterparty_credit_risk · market_risk · settlements_op_risk · regulatory_capital · reference_master</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Risk Data (CI, from schema)</t>
+          <t>Product owner</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -1381,19 +1381,19 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Logical warehouse layer. Set automatically based on schema.</t>
+          <t>Primary navigation axis. Drives marketplace organization.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>capability</t>
+          <t>archetype</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>collateral_management · liquidity_funding_risk · counterparty_credit_risk · market_risk · settlements_op_risk · regulatory_capital · reference_master</t>
+          <t>foundational · derived · consumer_aligned · conformed · reference · mart</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
@@ -1413,24 +1413,24 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Primary navigation axis. Drives marketplace organization.</t>
+          <t>Asset kind. foundational/derived/consumer_aligned for products.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>archetype</t>
+          <t>shape</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>foundational · derived · consumer_aligned · conformed · reference · mart</t>
+          <t>dim · fact · obt · lookup · view · mv · semantic_model</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -1445,24 +1445,24 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>Asset kind. foundational/derived/consumer_aligned for products.</t>
+          <t>Modeling shape. Useful for BI tool discovery.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>shape</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>dim · fact · obt · lookup · view · mv · semantic_model</t>
+          <t>draft · active · deprecated · sunset</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Recommended</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -1477,68 +1477,68 @@
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>Modeling shape. Useful for BI tool discovery.</t>
+          <t>Lifecycle status. deprecated triggers consumer notifications.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>draft · active · deprecated · sunset</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>SOURCE / PRODUCER (inherited from app)</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="23" t="n"/>
+      <c r="D10" s="23" t="n"/>
+      <c r="E10" s="23" t="n"/>
+      <c r="F10" s="24" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>source.app</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>app identifier — short lowercase (cmos, vs, rcs, xvala, liquidity, ...)</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Yes (foundational only)</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Risk Data (CI, inherited)</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Lifecycle status. deprecated triggers consumer notifications.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>SOURCE / PRODUCER (inherited from app)</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="n"/>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="23" t="n"/>
-      <c r="F11" s="24" t="n"/>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Producing app. Null for derived products spanning multiple apps.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>source.app</t>
+          <t>source.domain</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>app identifier — short lowercase (cmos, vs, rcs, xvala, liquidity, ...)</t>
+          <t>credit_risk · market_risk · funding · liquidity · shared</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Yes (foundational only)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1553,58 +1553,58 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Producing app. Null for derived products spanning multiple apps.</t>
+          <t>Product group catalog ("shared" for cross-domain).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>source.domain</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>credit_risk · market_risk · funding · liquidity · shared</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>OWNERSHIP</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="23" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="23" t="n"/>
+      <c r="F13" s="24" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>owner.business</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>team identifier</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Risk Data (CI, inherited)</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>Product group catalog ("shared" for cross-domain).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>OWNERSHIP</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="n"/>
-      <c r="C14" s="23" t="n"/>
-      <c r="D14" s="23" t="n"/>
-      <c r="E14" s="23" t="n"/>
-      <c r="F14" s="24" t="n"/>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Product owner</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Named accountable business role. Stable group, not individual.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>owner.business</t>
+          <t>owner.technical</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
@@ -1629,19 +1629,19 @@
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>Named accountable business role. Stable group, not individual.</t>
+          <t>Named accountable technical team.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>owner.technical</t>
+          <t>owner.email</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>team identifier</t>
+          <t>distribution list email</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -1661,63 +1661,63 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>Named accountable technical team.</t>
+          <t>Contact for questions, changes, incidents. Always a DL.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>owner.email</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>distribution list email</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>CLASSIFICATION (inherited &amp; enriched)</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="23" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="23" t="n"/>
+      <c r="F17" s="24" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>class.sensitivity</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>public · internal · confidential · restricted · mnpi</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>Contact for questions, changes, incidents. Always a DL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>CLASSIFICATION (inherited &amp; enriched)</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="n"/>
-      <c r="C18" s="23" t="n"/>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="23" t="n"/>
-      <c r="F18" s="24" t="n"/>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Risk Data (CI, highest of upstream)</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Sensitivity. Inherits highest of upstream sources.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>class.sensitivity</t>
+          <t>class.pii</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>public · internal · confidential · restricted · mnpi</t>
+          <t>true · false</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Risk Data (CI, highest of upstream)</t>
+          <t>Risk Data (CI, inherited)</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -1737,63 +1737,63 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Sensitivity. Inherits highest of upstream sources.</t>
+          <t>True if any column carries PII. Drives column masking.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>class.pii</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>true · false</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>CONTRACT</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="24" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>contract.version</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>semver (1.2.0)</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>Risk Data (CI, inherited)</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>True if any column carries PII. Drives column masking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>CONTRACT</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="n"/>
-      <c r="C21" s="23" t="n"/>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="23" t="n"/>
-      <c r="F21" s="24" t="n"/>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Risk Data (CI, from YAML)</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Version of published contract. Auto-set on YAML release.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>contract.version</t>
+          <t>contract.changed</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>semver (1.2.0)</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>Risk Data (CI, from YAML)</t>
+          <t>Risk Data (CI, auto)</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
@@ -1813,19 +1813,19 @@
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>Version of published contract. Auto-set on YAML release.</t>
+          <t>Date of last CONTRACT change (NOT data refresh).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>contract.changed</t>
+          <t>contract.ref</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>Confluence URL</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>Risk Data (CI, auto)</t>
+          <t>Product owner</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
@@ -1845,19 +1845,19 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>Date of last CONTRACT change (NOT data refresh).</t>
+          <t>URL of Confluence product page.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>contract.ref</t>
+          <t>grain</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>Confluence URL</t>
+          <t>composite key short form</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -1877,46 +1877,26 @@
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>URL of Confluence product page.</t>
+          <t>What one row represents. Short form for at-a-glance.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>grain</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>composite key short form</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>What one row represents. Short form for at-a-glance.</t>
-        </is>
-      </c>
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>OPERATIONAL</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="24" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>OPERATIONAL</t>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>refresh.freq</t>
         </is>
       </c>
       <c r="B26" s="23" t="n"/>
@@ -1928,12 +1908,12 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>refresh.freq</t>
+          <t>refresh.sla</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>intraday · daily · weekly · monthly · on_demand</t>
+          <t>string (e.g. daily_by_06:00_EST)</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -1953,46 +1933,26 @@
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>How often the data refreshes.</t>
+          <t>Specific time commitment.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>refresh.sla</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>string (e.g. daily_by_06:00_EST)</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>Specific time commitment.</t>
-        </is>
-      </c>
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>INTEGRATION</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="n"/>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="24" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>INTEGRATION</t>
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>collibra.ref</t>
         </is>
       </c>
       <c r="B29" s="23" t="n"/>
@@ -2001,46 +1961,15 @@
       <c r="E29" s="23" t="n"/>
       <c r="F29" s="24" t="n"/>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>collibra.ref</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>Collibra asset ID</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>Yes (when registered)</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="inlineStr">
-        <is>
-          <t>Cross-reference to enterprise catalog entry.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1"/>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="30" ht="22" customHeight="1"/>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>NOTE: ~18 table-level tags total for products. Of those, only ~10 are authored by humans (the product owner); the rest are inherited from the upstream app or auto-set by CI from the YAML contract. The YAML in Git is the source of truth — these tags are projections of it.</t>
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33" ht="40" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">

--- a/Confluence/uc_metadata_standards_v4.xlsx
+++ b/Confluence/uc_metadata_standards_v4.xlsx
@@ -9,13 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Rationale" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. App-layer tags" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Product-layer tags" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Column-level standards" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Column-level standards" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. App-layer tags'!$A$4:$G$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Product-layer tags'!$A$4:$G$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Column-level standards'!$A$4:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Column-level standards'!$A$4:$H$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -117,6 +115,11 @@
       <color rgb="001F4E78"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="001F4E78"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -181,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -236,6 +239,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -602,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -622,7 +628,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -835,6 +840,48 @@
       <c r="A42" s="9" t="inlineStr">
         <is>
           <t>This workbook covers UC tags for app-layer and product-layer tables. For the full data contract attribute specification (including YAML-only blocks like reference_dependencies, composability, currency_handling, known_issues), see data_contract_attribute_spec_v5.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Naming rule — namespace with four documented exceptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>All UC tag keys use dotted-namespace form (class.*, owner.*, source.*, contract.*, refresh.*, collibra.*, glossary.*, column.*) EXCEPT four bare keys that are heavily filtered and benefit from brevity:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • capability  • archetype  • shape  • status</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>These four are the top-level classifiers used most often in catalog filters, dashboards, and policies. Brevity matters for them. Every other tag follows the namespace rule including grain (now contract.grain).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Where product attributes live</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>This workbook covers UC tags for app-layer tables and column-level standards. For product authoring (both foundational and derived contracts), the single source of truth is data_contract_attribute_spec_v5.xlsx. That spec lists every contract attribute with a UC-tag column — filter by 'UC tag' to see exactly the subset that becomes tags.</t>
         </is>
       </c>
     </row>
@@ -1235,759 +1282,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PRODUCT-LAYER TAGS (table level)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Applied on tables in risk_warehouse (core, analytics, products schemas). Yellow rows are inherited from the upstream app — set automatically by CI, not re-authored. Filter the Category column to focus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Tag key</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Allowed values</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Required?</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Authored by</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Inherited from app?</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>capability</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>collateral_management · liquidity_funding_risk · counterparty_credit_risk · market_risk · settlements_op_risk · regulatory_capital · reference_master</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>Primary navigation axis. Drives marketplace organization.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>archetype</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>foundational · derived · consumer_aligned · conformed · reference · mart</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>Asset kind. foundational/derived/consumer_aligned for products.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>shape</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>dim · fact · obt · lookup · view · mv · semantic_model</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>Modeling shape. Useful for BI tool discovery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>draft · active · deprecated · sunset</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>Lifecycle status. deprecated triggers consumer notifications.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>source.app</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>SOURCE / PRODUCER</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>app identifier — short lowercase (cmos, vs, rcs, xvala, liquidity, ...)</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>Yes (foundational only)</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Risk Data (CI, inherited)</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>Producing app. Null for derived products spanning multiple apps.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>source.domain</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>SOURCE / PRODUCER</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>credit_risk · market_risk · funding · liquidity · shared</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Risk Data (CI, inherited)</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>Product group catalog ("shared" for cross-domain).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>owner.business</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>OWNERSHIP</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>team identifier</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>Named accountable business role. Stable group, not individual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>owner.technical</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>OWNERSHIP</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>team identifier</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>Named accountable technical team.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>owner.email</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>OWNERSHIP</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>distribution list email</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>Contact for questions, changes, incidents. Always a DL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>class.sensitivity</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>CLASSIFICATION</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>public · internal · confidential · restricted · mnpi</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>Risk Data (CI, highest of upstream)</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>Sensitivity. Inherits highest of upstream sources.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>class.pii</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>CLASSIFICATION</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>true · false</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Risk Data (CI, inherited)</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>True if any column carries PII. Drives column masking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>contract.version</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>CONTRACT</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>semver (1.2.0)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>Risk Data (CI, from YAML)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>Version of published contract. Auto-set on YAML release.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>contract.changed</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>CONTRACT</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>Risk Data (CI, auto)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>Date of last CONTRACT change (NOT data refresh).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>contract.ref</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>CONTRACT</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>Confluence URL</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>URL of Confluence product page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>grain</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>CONTRACT</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>composite key short form</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>What one row represents. Short form for at-a-glance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>refresh.freq</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>OPERATIONAL</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>intraday · daily · weekly · monthly · on_demand</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>How often the data refreshes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>refresh.sla</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>OPERATIONAL</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>string (e.g. daily_by_06:00_EST)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>Specific time commitment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>collibra.ref</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>INTEGRATION</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>Collibra asset ID</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>Yes (when registered)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>Product owner</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>Cross-reference to enterprise catalog entry.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="75" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>~17 table-level tags total for products. Of those, only ~10 are authored by humans (the product owner); the rest are inherited from the upstream app or auto-set by CI from the YAML contract. The YAML in Git is the source of truth — these tags are projections of it. For the full contract attribute set (including reference_dependencies, composability, currency_handling, known_issues which are YAML-only), see data_contract_attribute_spec_v5.xlsx.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:G22"/>
-  <mergeCells count="3">
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
